--- a/data/trans_dic/AIRE_1_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/AIRE_1_R-Habitat-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no está dispuesta a pagar para reducir la contaminación del aire (impuesto durante 5 años)</t>
+          <t>Población que no está dispuesta a pagar para reducir la contaminación del aire (impuesto durante 5 años) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>66,93; 77,45</t>
+          <t>67,64; 77,75</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>71,47; 78,52</t>
+          <t>71,47; 78,58</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>70,66; 77,22</t>
+          <t>70,9; 77,16</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>66,52; 76,54</t>
+          <t>66,9; 76,3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>72,15; 79,35</t>
+          <t>72,54; 79,52</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>70,86; 77,09</t>
+          <t>70,89; 76,77</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>65,21; 77,29</t>
+          <t>65,72; 77,54</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>59,35; 92,09</t>
+          <t>59,79; 92,75</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>65,09; 88,72</t>
+          <t>65,14; 87,62</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>71,85; 80,33</t>
+          <t>71,51; 80,54</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>78,31; 84,24</t>
+          <t>78,16; 84,09</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>76,47; 81,33</t>
+          <t>76,6; 81,48</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>70,89; 76,0</t>
+          <t>70,85; 75,95</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>73,6; 84,43</t>
+          <t>73,65; 84,14</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>73,35; 80,19</t>
+          <t>73,41; 80,12</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no está dispuesta a pagar para reducir la contaminación del aire (impuesto durante 5 años)</t>
+          <t>Población que no está dispuesta a pagar para reducir la contaminación del aire (impuesto durante 5 años) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>232892; 269498</t>
+          <t>235366; 270541</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>253566; 278575</t>
+          <t>253552; 278775</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>496580; 542650</t>
+          <t>498261; 542235</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>332903; 383006</t>
+          <t>334768; 381817</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>345562; 380009</t>
+          <t>347428; 380861</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>693925; 754947</t>
+          <t>694287; 751803</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>216138; 256183</t>
+          <t>217811; 256998</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>323184; 501476</t>
+          <t>325552; 505040</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>570169; 777200</t>
+          <t>570626; 767502</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>341456; 381750</t>
+          <t>339828; 382750</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>414703; 446075</t>
+          <t>413905; 445317</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>768351; 817178</t>
+          <t>769682; 818697</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1173195; 1257849</t>
+          <t>1172583; 1257039</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1404113; 1610666</t>
+          <t>1405072; 1605310</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2613514; 2857112</t>
+          <t>2615583; 2854479</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/AIRE_1_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/AIRE_1_R-Habitat-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>73,04%</t>
+          <t>73,44%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>75,22%</t>
+          <t>75,44%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>74,14%</t>
+          <t>74,45%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>67,64; 77,75</t>
+          <t>68,06; 77,76</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>71,47; 78,58</t>
+          <t>71,95; 78,8</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>70,9; 77,16</t>
+          <t>71,51; 77,34</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>72,0%</t>
+          <t>72,65%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>76,28%</t>
+          <t>77,07%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>74,09%</t>
+          <t>74,85%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>66,9; 76,3</t>
+          <t>67,47; 76,48</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>72,54; 79,52</t>
+          <t>73,49; 80,58</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>70,89; 76,77</t>
+          <t>71,5; 77,33</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>72,2%</t>
+          <t>71,19%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>77,5%</t>
+          <t>70,63%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>75,49%</t>
+          <t>70,92%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>65,72; 77,54</t>
+          <t>65,21; 76,31</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>59,79; 92,75</t>
+          <t>65,73; 74,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>65,14; 87,62</t>
+          <t>67,6; 74,85</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>76,64%</t>
+          <t>77,57%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>81,35%</t>
+          <t>81,4%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>79,12%</t>
+          <t>79,6%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>71,51; 80,54</t>
+          <t>73,66; 81,36</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>78,16; 84,09</t>
+          <t>78,38; 83,88</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>76,6; 81,48</t>
+          <t>77,21; 81,71</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>73,59%</t>
+          <t>73,91%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>77,84%</t>
+          <t>76,82%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>75,87%</t>
+          <t>75,39%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>70,85; 75,95</t>
+          <t>71,31; 76,06</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>73,65; 84,14</t>
+          <t>74,97; 78,56</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>73,41; 80,12</t>
+          <t>73,95; 76,8</t>
         </is>
       </c>
     </row>
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>254144</t>
+          <t>277179</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>266850</t>
+          <t>287717</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>520994</t>
+          <t>564896</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>235366; 270541</t>
+          <t>256872; 293487</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>253552; 278775</t>
+          <t>274428; 300521</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>498261; 542235</t>
+          <t>542603; 586853</t>
         </is>
       </c>
     </row>
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>360288</t>
+          <t>390125</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>365335</t>
+          <t>408681</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>725624</t>
+          <t>798807</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>334768; 381817</t>
+          <t>362324; 410683</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>347428; 380861</t>
+          <t>389719; 427296</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>694287; 751803</t>
+          <t>763117; 825276</t>
         </is>
       </c>
     </row>
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>239318</t>
+          <t>266447</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>421997</t>
+          <t>257725</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>661315</t>
+          <t>524172</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>217811; 256998</t>
+          <t>244056; 285591</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>325552; 505040</t>
+          <t>239816; 272591</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>570626; 767502</t>
+          <t>499663; 553244</t>
         </is>
       </c>
     </row>
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>364196</t>
+          <t>397479</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>430820</t>
+          <t>472040</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>795017</t>
+          <t>869520</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>339828; 382750</t>
+          <t>377452; 416929</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>413905; 445317</t>
+          <t>454565; 486458</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>769682; 818697</t>
+          <t>843453; 892613</t>
         </is>
       </c>
     </row>
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1217946</t>
+          <t>1331230</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1485002</t>
+          <t>1426164</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2702949</t>
+          <t>2757393</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1172583; 1257039</t>
+          <t>1284265; 1369981</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1405072; 1605310</t>
+          <t>1391742; 1458383</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2615583; 2854479</t>
+          <t>2704879; 2809037</t>
         </is>
       </c>
     </row>
